--- a/artfynd/A 1477-2024 artfynd.xlsx
+++ b/artfynd/A 1477-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127898352</v>
+        <v>137435126</v>
       </c>
       <c r="B2" t="n">
-        <v>56845</v>
+        <v>87436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100053</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>624 55 Gotlands kommun, Gtl</t>
+          <t>Kullshage S, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721371</v>
+        <v>721289</v>
       </c>
       <c r="R2" t="n">
-        <v>6416505</v>
+        <v>6416576</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,28 +775,4233 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435126</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137435129</v>
+      </c>
+      <c r="B3" t="n">
+        <v>87436</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>424</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>721281</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6416502</v>
+      </c>
+      <c r="S3" t="n">
+        <v>18</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435129</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137435140</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87611</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>449</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>721224</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6416458</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435140</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137435153</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87611</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>449</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>721217</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6416526</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435153</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137435117</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>721436</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6416538</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435117</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137435123</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>721329</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6416580</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435123</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137435130</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>721289</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6416481</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435130</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137435144</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>721209</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6416606</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435144</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137435149</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>721191</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6416622</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435149</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137435113</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96642</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>721467</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6416533</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435113</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137435118</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91614</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>721352</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6416563</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435118</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137435151</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91614</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>721182</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6416598</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435151</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137435119</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87413</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>721357</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6416558</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435119</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137435121</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87413</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>721347</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6416567</v>
+      </c>
+      <c r="S15" t="n">
+        <v>12</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435121</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137435127</v>
+      </c>
+      <c r="B16" t="n">
+        <v>87413</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>721278</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6416576</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435127</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137435146</v>
+      </c>
+      <c r="B17" t="n">
+        <v>87413</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>721217</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6416667</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435146</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137435150</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87413</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>721184</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6416616</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435150</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137435134</v>
+      </c>
+      <c r="B19" t="n">
+        <v>89390</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>721279</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6416438</v>
+      </c>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435134</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137435135</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93152</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>721276</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6416436</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435135</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137435108</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>721491</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6416512</v>
+      </c>
+      <c r="S21" t="n">
+        <v>12</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435108</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137435115</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>721443</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6416550</v>
+      </c>
+      <c r="S22" t="n">
+        <v>14</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435115</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137435132</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>721274</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6416463</v>
+      </c>
+      <c r="S23" t="n">
+        <v>12</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435132</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137435152</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>721199</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6416544</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435152</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127898352</v>
+      </c>
+      <c r="B25" t="n">
+        <v>56845</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>624 55 Gotlands kommun, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>721371</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6416505</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Johan Möller</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Via Johan Möller</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY25" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127898352</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137435147</v>
+      </c>
+      <c r="B26" t="n">
+        <v>111745</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>721219</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6416667</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435147</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137435112</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99405</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>721471</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6416533</v>
+      </c>
+      <c r="S27" t="n">
+        <v>11</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435112</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137435114</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99453</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>721466</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6416531</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435114</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137435133</v>
+      </c>
+      <c r="B29" t="n">
+        <v>107862</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>721288</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6416439</v>
+      </c>
+      <c r="S29" t="n">
+        <v>11</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435133</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137435109</v>
+      </c>
+      <c r="B30" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>721489</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6416512</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435109</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137435111</v>
+      </c>
+      <c r="B31" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>721462</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6416523</v>
+      </c>
+      <c r="S31" t="n">
+        <v>11</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435111</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137435116</v>
+      </c>
+      <c r="B32" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>721436</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6416538</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435116</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137435125</v>
+      </c>
+      <c r="B33" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>721283</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6416578</v>
+      </c>
+      <c r="S33" t="n">
+        <v>12</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435125</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137435128</v>
+      </c>
+      <c r="B34" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>721289</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6416549</v>
+      </c>
+      <c r="S34" t="n">
+        <v>7</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435128</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137435143</v>
+      </c>
+      <c r="B35" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>721186</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6416540</v>
+      </c>
+      <c r="S35" t="n">
+        <v>16</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435143</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137435145</v>
+      </c>
+      <c r="B36" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>721227</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6416645</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435145</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137435148</v>
+      </c>
+      <c r="B37" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>721200</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6416681</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435148</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137435155</v>
+      </c>
+      <c r="B38" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>721207</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6416479</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435155</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137435110</v>
+      </c>
+      <c r="B39" t="n">
+        <v>87617</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6052416</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fågelträcksspindling</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cortinarius subrugulosus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bidaud &amp; Armada</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>721464</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6416538</v>
+      </c>
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435110</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1477-2024 artfynd.xlsx
+++ b/artfynd/A 1477-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ39"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137435126</v>
       </c>
       <c r="B2" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137435129</v>
       </c>
       <c r="B3" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137435140</v>
       </c>
       <c r="B4" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137435153</v>
       </c>
       <c r="B5" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137435117</v>
       </c>
       <c r="B6" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137435123</v>
       </c>
       <c r="B7" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137435130</v>
       </c>
       <c r="B8" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137435144</v>
       </c>
       <c r="B9" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137435149</v>
       </c>
       <c r="B10" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,48 +1688,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137435113</v>
+        <v>137445155</v>
       </c>
       <c r="B11" t="n">
-        <v>96642</v>
+        <v>91963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2812</v>
+        <v>2015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullshage S, Gtl</t>
+          <t>Träskmyr- Västeån, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721467</v>
+        <v>721254</v>
       </c>
       <c r="R11" t="n">
-        <v>6416533</v>
+        <v>6416560</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,89 +1759,83 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435113</t>
+          <t>https://artportalen.se/Sighting/137445155</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137435118</v>
+        <v>137445412</v>
       </c>
       <c r="B12" t="n">
-        <v>91614</v>
+        <v>91963</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3286</v>
+        <v>2015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kullshage S, Gtl</t>
+          <t>Träskmyr- Västeån, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721352</v>
+        <v>721265</v>
       </c>
       <c r="R12" t="n">
-        <v>6416563</v>
+        <v>6416502</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,76 +1865,67 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435118</t>
+          <t>https://artportalen.se/Sighting/137445412</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137435151</v>
+        <v>137435113</v>
       </c>
       <c r="B13" t="n">
-        <v>91614</v>
+        <v>96643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3286</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1935,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721182</v>
+        <v>721467</v>
       </c>
       <c r="R13" t="n">
-        <v>6416598</v>
+        <v>6416533</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1982,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,16 +2006,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435151</t>
+          <t>https://artportalen.se/Sighting/137435113</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137435119</v>
+        <v>137435118</v>
       </c>
       <c r="B14" t="n">
-        <v>87413</v>
+        <v>91615</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +2023,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3712</v>
+        <v>3286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721357</v>
+        <v>721352</v>
       </c>
       <c r="R14" t="n">
-        <v>6416558</v>
+        <v>6416563</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,16 +2118,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435119</t>
+          <t>https://artportalen.se/Sighting/137435118</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137435121</v>
+        <v>137435151</v>
       </c>
       <c r="B15" t="n">
-        <v>87413</v>
+        <v>91615</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +2135,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3712</v>
+        <v>3286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,13 +2159,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721347</v>
+        <v>721182</v>
       </c>
       <c r="R15" t="n">
-        <v>6416567</v>
+        <v>6416598</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,7 +2213,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2243,54 +2230,57 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435121</t>
+          <t>https://artportalen.se/Sighting/137435151</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137435127</v>
+        <v>137445338</v>
       </c>
       <c r="B16" t="n">
-        <v>87413</v>
+        <v>87553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullshage S, Gtl</t>
+          <t>Träskmyr- Västeån, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721278</v>
+        <v>721254</v>
       </c>
       <c r="R16" t="n">
-        <v>6416576</v>
+        <v>6416560</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2317,19 +2307,9 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,27 +2325,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435127</t>
+          <t>https://artportalen.se/Sighting/137445338</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137435146</v>
+        <v>137435119</v>
       </c>
       <c r="B17" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,13 +2377,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721217</v>
+        <v>721357</v>
       </c>
       <c r="R17" t="n">
-        <v>6416667</v>
+        <v>6416558</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2432,7 +2412,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2442,7 +2422,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,16 +2448,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435146</t>
+          <t>https://artportalen.se/Sighting/137435119</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137435150</v>
+        <v>137435121</v>
       </c>
       <c r="B18" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,13 +2489,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721184</v>
+        <v>721347</v>
       </c>
       <c r="R18" t="n">
-        <v>6416616</v>
+        <v>6416567</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2544,7 +2524,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2554,7 +2534,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2581,38 +2561,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435150</t>
+          <t>https://artportalen.se/Sighting/137435121</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137435134</v>
+        <v>137435127</v>
       </c>
       <c r="B19" t="n">
-        <v>89390</v>
+        <v>87414</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4405</v>
+        <v>3712</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2622,13 +2602,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721279</v>
+        <v>721278</v>
       </c>
       <c r="R19" t="n">
-        <v>6416438</v>
+        <v>6416576</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2657,7 +2637,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2667,14 +2647,14 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
@@ -2694,38 +2674,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435134</t>
+          <t>https://artportalen.se/Sighting/137435127</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137435135</v>
+        <v>137435146</v>
       </c>
       <c r="B20" t="n">
-        <v>93152</v>
+        <v>87414</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>3712</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721276</v>
+        <v>721217</v>
       </c>
       <c r="R20" t="n">
-        <v>6416436</v>
+        <v>6416667</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2770,7 +2750,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2760,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,38 +2786,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435135</t>
+          <t>https://artportalen.se/Sighting/137435146</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137435108</v>
+        <v>137435150</v>
       </c>
       <c r="B21" t="n">
-        <v>58032</v>
+        <v>87414</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>3712</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2847,13 +2827,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721491</v>
+        <v>721184</v>
       </c>
       <c r="R21" t="n">
-        <v>6416512</v>
+        <v>6416616</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2882,7 +2862,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2872,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,6 +2881,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2918,54 +2899,57 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435108</t>
+          <t>https://artportalen.se/Sighting/137435150</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137435115</v>
+        <v>137445332</v>
       </c>
       <c r="B22" t="n">
-        <v>58032</v>
+        <v>87414</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>3712</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kullshage S, Gtl</t>
+          <t>Träskmyr- Västeån, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721443</v>
+        <v>721254</v>
       </c>
       <c r="R22" t="n">
-        <v>6416550</v>
+        <v>6416560</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2992,54 +2976,45 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435115</t>
+          <t>https://artportalen.se/Sighting/137445332</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137435132</v>
+        <v>137435134</v>
       </c>
       <c r="B23" t="n">
-        <v>58032</v>
+        <v>89391</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,21 +3022,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>4405</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3046,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721274</v>
+        <v>721279</v>
       </c>
       <c r="R23" t="n">
-        <v>6416463</v>
+        <v>6416438</v>
       </c>
       <c r="S23" t="n">
         <v>12</v>
@@ -3106,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3116,15 +3091,16 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3142,16 +3118,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435132</t>
+          <t>https://artportalen.se/Sighting/137435134</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137435152</v>
+        <v>137435135</v>
       </c>
       <c r="B24" t="n">
-        <v>58032</v>
+        <v>93153</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,21 +3135,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3183,10 +3159,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721199</v>
+        <v>721276</v>
       </c>
       <c r="R24" t="n">
-        <v>6416544</v>
+        <v>6416436</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3218,7 +3194,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3228,7 +3204,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,63 +3230,54 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435152</t>
+          <t>https://artportalen.se/Sighting/137435135</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127898352</v>
+        <v>137435108</v>
       </c>
       <c r="B25" t="n">
-        <v>56845</v>
+        <v>58032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100053</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>624 55 Gotlands kommun, Gtl</t>
+          <t>Kullshage S, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721371</v>
+        <v>721491</v>
       </c>
       <c r="R25" t="n">
-        <v>6416505</v>
+        <v>6416512</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3334,22 +3301,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3364,53 +3331,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127898352</t>
+          <t>https://artportalen.se/Sighting/137435108</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137435147</v>
+        <v>137435115</v>
       </c>
       <c r="B26" t="n">
-        <v>111745</v>
+        <v>58032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3420,13 +3383,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721219</v>
+        <v>721443</v>
       </c>
       <c r="R26" t="n">
-        <v>6416667</v>
+        <v>6416550</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3455,7 +3418,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3465,16 +3428,15 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3492,16 +3454,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435147</t>
+          <t>https://artportalen.se/Sighting/137435115</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137435112</v>
+        <v>137435132</v>
       </c>
       <c r="B27" t="n">
-        <v>99405</v>
+        <v>58032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3509,21 +3471,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219797</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3533,13 +3495,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721471</v>
+        <v>721274</v>
       </c>
       <c r="R27" t="n">
-        <v>6416533</v>
+        <v>6416463</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,7 +3530,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3578,7 +3540,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3604,16 +3566,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435112</t>
+          <t>https://artportalen.se/Sighting/137435132</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137435114</v>
+        <v>137435152</v>
       </c>
       <c r="B28" t="n">
-        <v>99453</v>
+        <v>58032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,21 +3583,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219862</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3645,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721466</v>
+        <v>721199</v>
       </c>
       <c r="R28" t="n">
-        <v>6416531</v>
+        <v>6416544</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3680,7 +3642,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3690,7 +3652,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3716,54 +3678,63 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435114</t>
+          <t>https://artportalen.se/Sighting/137435152</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137435133</v>
+        <v>127898352</v>
       </c>
       <c r="B29" t="n">
-        <v>107862</v>
+        <v>56845</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>100053</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kullshage S, Gtl</t>
+          <t>624 55 Gotlands kommun, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721288</v>
+        <v>721371</v>
       </c>
       <c r="R29" t="n">
-        <v>6416439</v>
+        <v>6416505</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3787,22 +3758,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3817,27 +3788,31 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435133</t>
+          <t>https://artportalen.se/Sighting/127898352</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137435109</v>
+        <v>137435147</v>
       </c>
       <c r="B30" t="n">
-        <v>87589</v>
+        <v>111746</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,21 +3820,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003295</v>
+        <v>219711</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3869,13 +3844,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721489</v>
+        <v>721219</v>
       </c>
       <c r="R30" t="n">
-        <v>6416512</v>
+        <v>6416667</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3904,7 +3879,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3914,14 +3889,14 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
@@ -3941,38 +3916,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435109</t>
+          <t>https://artportalen.se/Sighting/137435147</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137435111</v>
+        <v>137435112</v>
       </c>
       <c r="B31" t="n">
-        <v>87589</v>
+        <v>99406</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6003295</v>
+        <v>219797</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3982,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721462</v>
+        <v>721471</v>
       </c>
       <c r="R31" t="n">
-        <v>6416523</v>
+        <v>6416533</v>
       </c>
       <c r="S31" t="n">
         <v>11</v>
@@ -4017,7 +3992,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4027,7 +4002,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4036,7 +4011,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4054,54 +4028,58 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435111</t>
+          <t>https://artportalen.se/Sighting/137435112</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137435116</v>
+        <v>137445370</v>
       </c>
       <c r="B32" t="n">
-        <v>87589</v>
+        <v>99406</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6003295</v>
+        <v>219797</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kullshage S, Gtl</t>
+          <t>Träskmyr- Västeån, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721436</v>
+        <v>721190</v>
       </c>
       <c r="R32" t="n">
-        <v>6416538</v>
+        <v>6416517</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4128,19 +4106,9 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4156,65 +4124,69 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435116</t>
+          <t>https://artportalen.se/Sighting/137445370</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137435125</v>
+        <v>137445342</v>
       </c>
       <c r="B33" t="n">
-        <v>87589</v>
+        <v>99409</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>219798</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kullshage S, Gtl</t>
+          <t>Träskmyr- Västeån, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721283</v>
+        <v>721254</v>
       </c>
       <c r="R33" t="n">
-        <v>6416578</v>
+        <v>6416560</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4241,19 +4213,9 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4269,49 +4231,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435125</t>
+          <t>https://artportalen.se/Sighting/137445342</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137435128</v>
+        <v>137435114</v>
       </c>
       <c r="B34" t="n">
-        <v>87589</v>
+        <v>99454</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4321,13 +4283,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721289</v>
+        <v>721466</v>
       </c>
       <c r="R34" t="n">
-        <v>6416549</v>
+        <v>6416531</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4356,7 +4318,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4366,7 +4328,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4375,7 +4337,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4393,54 +4354,58 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435128</t>
+          <t>https://artportalen.se/Sighting/137435114</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137435143</v>
+        <v>137445359</v>
       </c>
       <c r="B35" t="n">
-        <v>87589</v>
+        <v>107155</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6003295</v>
+        <v>220785</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kullshage S, Gtl</t>
+          <t>Träskmyr- Västeån, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721186</v>
+        <v>721185</v>
       </c>
       <c r="R35" t="n">
-        <v>6416540</v>
+        <v>6416566</v>
       </c>
       <c r="S35" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4467,19 +4432,14 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:22</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Småträd</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,65 +4455,69 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435143</t>
+          <t>https://artportalen.se/Sighting/137445359</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137435145</v>
+        <v>137445439</v>
       </c>
       <c r="B36" t="n">
-        <v>87589</v>
+        <v>99431</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kullshage S, Gtl</t>
+          <t>Träskmyr- Västeån, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721227</v>
+        <v>721311</v>
       </c>
       <c r="R36" t="n">
-        <v>6416645</v>
+        <v>6416491</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4580,19 +4544,14 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:26</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ett trettiotal</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4608,65 +4567,69 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435145</t>
+          <t>https://artportalen.se/Sighting/137445439</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137435148</v>
+        <v>137445427</v>
       </c>
       <c r="B37" t="n">
-        <v>87589</v>
+        <v>106585</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kullshage S, Gtl</t>
+          <t>Träskmyr- Västeån, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>721200</v>
+        <v>721260</v>
       </c>
       <c r="R37" t="n">
-        <v>6416681</v>
+        <v>6416510</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4693,19 +4656,14 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:28</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4721,27 +4679,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435148</t>
+          <t>https://artportalen.se/Sighting/137445427</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137435155</v>
+        <v>137435133</v>
       </c>
       <c r="B38" t="n">
-        <v>87589</v>
+        <v>107863</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4749,21 +4707,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4773,13 +4731,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721207</v>
+        <v>721288</v>
       </c>
       <c r="R38" t="n">
-        <v>6416479</v>
+        <v>6416439</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4808,7 +4766,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4818,7 +4776,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4827,7 +4785,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4845,38 +4802,38 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137435155</t>
+          <t>https://artportalen.se/Sighting/137435133</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137435110</v>
+        <v>137435109</v>
       </c>
       <c r="B39" t="n">
-        <v>87617</v>
+        <v>87590</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6052416</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fågelträcksspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius subrugulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bidaud &amp; Armada</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4886,13 +4843,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721464</v>
+        <v>721489</v>
       </c>
       <c r="R39" t="n">
-        <v>6416538</v>
+        <v>6416512</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4921,7 +4878,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4931,14 +4888,14 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
@@ -4957,6 +4914,1023 @@
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435109</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137435111</v>
+      </c>
+      <c r="B40" t="n">
+        <v>87590</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>721462</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6416523</v>
+      </c>
+      <c r="S40" t="n">
+        <v>11</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435111</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137435116</v>
+      </c>
+      <c r="B41" t="n">
+        <v>87590</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>721436</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6416538</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435116</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137435125</v>
+      </c>
+      <c r="B42" t="n">
+        <v>87590</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>721283</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6416578</v>
+      </c>
+      <c r="S42" t="n">
+        <v>12</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435125</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137435128</v>
+      </c>
+      <c r="B43" t="n">
+        <v>87590</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>721289</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6416549</v>
+      </c>
+      <c r="S43" t="n">
+        <v>7</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435128</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137435143</v>
+      </c>
+      <c r="B44" t="n">
+        <v>87590</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>721186</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6416540</v>
+      </c>
+      <c r="S44" t="n">
+        <v>16</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435143</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137435145</v>
+      </c>
+      <c r="B45" t="n">
+        <v>87590</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>721227</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6416645</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435145</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137435148</v>
+      </c>
+      <c r="B46" t="n">
+        <v>87590</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>721200</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6416681</v>
+      </c>
+      <c r="S46" t="n">
+        <v>8</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435148</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137435155</v>
+      </c>
+      <c r="B47" t="n">
+        <v>87590</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>721207</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6416479</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137435155</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137435110</v>
+      </c>
+      <c r="B48" t="n">
+        <v>87618</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6052416</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fågelträcksspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius subrugulosus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bidaud &amp; Armada</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kullshage S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>721464</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6416538</v>
+      </c>
+      <c r="S48" t="n">
+        <v>9</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137435110</t>
         </is>
@@ -5002,6 +5976,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1477-2024 artfynd.xlsx
+++ b/artfynd/A 1477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137435126</v>
       </c>
       <c r="B2" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137435129</v>
       </c>
       <c r="B3" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137435140</v>
       </c>
       <c r="B4" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137435153</v>
       </c>
       <c r="B5" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137435117</v>
       </c>
       <c r="B6" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137435123</v>
       </c>
       <c r="B7" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137435130</v>
       </c>
       <c r="B8" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137435144</v>
       </c>
       <c r="B9" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137435149</v>
       </c>
       <c r="B10" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137445155</v>
       </c>
       <c r="B11" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>137445412</v>
       </c>
       <c r="B12" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>137435113</v>
       </c>
       <c r="B13" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>137435118</v>
       </c>
       <c r="B14" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>137435151</v>
       </c>
       <c r="B15" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>137445338</v>
       </c>
       <c r="B16" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137435119</v>
       </c>
       <c r="B17" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>137435121</v>
       </c>
       <c r="B18" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>137435127</v>
       </c>
       <c r="B19" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>137435146</v>
       </c>
       <c r="B20" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>137435150</v>
       </c>
       <c r="B21" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>137445332</v>
       </c>
       <c r="B22" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>137435134</v>
       </c>
       <c r="B23" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>137435135</v>
       </c>
       <c r="B24" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137435147</v>
       </c>
       <c r="B30" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>137435112</v>
       </c>
       <c r="B31" t="n">
-        <v>99406</v>
+        <v>99409</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>137445370</v>
       </c>
       <c r="B32" t="n">
-        <v>99406</v>
+        <v>99409</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>137445342</v>
       </c>
       <c r="B33" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>137435114</v>
       </c>
       <c r="B34" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>137445359</v>
       </c>
       <c r="B35" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>137445439</v>
       </c>
       <c r="B36" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>137445427</v>
       </c>
       <c r="B37" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>137435133</v>
       </c>
       <c r="B38" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>137435109</v>
       </c>
       <c r="B39" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>137435111</v>
       </c>
       <c r="B40" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>137435116</v>
       </c>
       <c r="B41" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>137435125</v>
       </c>
       <c r="B42" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137435128</v>
       </c>
       <c r="B43" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>137435143</v>
       </c>
       <c r="B44" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>137435145</v>
       </c>
       <c r="B45" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>137435148</v>
       </c>
       <c r="B46" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>137435155</v>
       </c>
       <c r="B47" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>137435110</v>
       </c>
       <c r="B48" t="n">
-        <v>87618</v>
+        <v>87621</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 1477-2024 artfynd.xlsx
+++ b/artfynd/A 1477-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137435126</v>
       </c>
       <c r="B2" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137435129</v>
       </c>
       <c r="B3" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137435140</v>
       </c>
       <c r="B4" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137435153</v>
       </c>
       <c r="B5" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137435117</v>
       </c>
       <c r="B6" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137435123</v>
       </c>
       <c r="B7" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137435130</v>
       </c>
       <c r="B8" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137435144</v>
       </c>
       <c r="B9" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137435149</v>
       </c>
       <c r="B10" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137445155</v>
       </c>
       <c r="B11" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>137445412</v>
       </c>
       <c r="B12" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>137435113</v>
       </c>
       <c r="B13" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>137435118</v>
       </c>
       <c r="B14" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>137435151</v>
       </c>
       <c r="B15" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>137445338</v>
       </c>
       <c r="B16" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137435119</v>
       </c>
       <c r="B17" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>137435121</v>
       </c>
       <c r="B18" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>137435127</v>
       </c>
       <c r="B19" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>137435146</v>
       </c>
       <c r="B20" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>137435150</v>
       </c>
       <c r="B21" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>137445332</v>
       </c>
       <c r="B22" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>137435134</v>
       </c>
       <c r="B23" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>137435135</v>
       </c>
       <c r="B24" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>137435108</v>
       </c>
       <c r="B25" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137435115</v>
       </c>
       <c r="B26" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>137435132</v>
       </c>
       <c r="B27" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>137435152</v>
       </c>
       <c r="B28" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137435147</v>
       </c>
       <c r="B30" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>137435112</v>
       </c>
       <c r="B31" t="n">
-        <v>99409</v>
+        <v>99413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>137445370</v>
       </c>
       <c r="B32" t="n">
-        <v>99409</v>
+        <v>99413</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>137445342</v>
       </c>
       <c r="B33" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>137435114</v>
       </c>
       <c r="B34" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>137445359</v>
       </c>
       <c r="B35" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>137445439</v>
       </c>
       <c r="B36" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>137445427</v>
       </c>
       <c r="B37" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>137435133</v>
       </c>
       <c r="B38" t="n">
-        <v>107866</v>
+        <v>107872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>137435109</v>
       </c>
       <c r="B39" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>137435111</v>
       </c>
       <c r="B40" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>137435116</v>
       </c>
       <c r="B41" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>137435125</v>
       </c>
       <c r="B42" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137435128</v>
       </c>
       <c r="B43" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>137435143</v>
       </c>
       <c r="B44" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>137435145</v>
       </c>
       <c r="B45" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>137435148</v>
       </c>
       <c r="B46" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>137435155</v>
       </c>
       <c r="B47" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>137435110</v>
       </c>
       <c r="B48" t="n">
-        <v>87621</v>
+        <v>87625</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
